--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:16</t>
+    <t xml:space="preserve">2026-09-09 23:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:11</t>
+    <t xml:space="preserve">2026-09-17 14:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:07</t>
+    <t xml:space="preserve">2026-09-23 12:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:36</t>
+    <t xml:space="preserve">2026-10-02 14:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2022_tarapaca.xlsx
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:24</t>
+    <t xml:space="preserve">2026-10-05 10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>442212.62</v>
+        <v>442212.63</v>
       </c>
     </row>
     <row r="3">
